--- a/3. Hardware/Self-evaluation-checklist.xlsx
+++ b/3. Hardware/Self-evaluation-checklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAMBRIDGE IGCSE &amp; O LEVEL COMPUTER SCIENCE\3. Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E723D7AF-EA7C-44B5-A9F8-8A95D29A1141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB17A7E-8213-4BFC-B0CB-D07E01371688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{702BB0E8-E787-4C75-8E53-536BC6E6ED30}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t xml:space="preserve">I can </t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>explain the advantages and disadvantages of storing data in cloud, rather than storing locally.</t>
+  </si>
+  <si>
+    <t>●</t>
   </si>
 </sst>
 </file>
@@ -142,7 +145,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,6 +167,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -195,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -207,16 +216,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,7 +595,9 @@
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="7"/>
+      <c r="E2" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -598,7 +608,9 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -609,7 +621,9 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
@@ -620,7 +634,9 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -631,7 +647,9 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -642,7 +660,9 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -653,7 +673,9 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -664,7 +686,9 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
@@ -675,7 +699,9 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -686,7 +712,9 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
@@ -697,7 +725,9 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -708,7 +738,9 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
@@ -719,7 +751,9 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
@@ -730,7 +764,9 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
@@ -741,7 +777,9 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
@@ -752,7 +790,9 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="8"/>
+      <c r="E17" s="7" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
